--- a/ig/test-tabs-svs/ValueSet-jdv-j392-type-courrier-ms.xlsx
+++ b/ig/test-tabs-svs/ValueSet-jdv-j392-type-courrier-ms.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="55">
   <si>
     <t>Property</t>
   </si>
@@ -135,9 +135,6 @@
   </si>
   <si>
     <t>warning-draft</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j392-type-courrier-ms|20260505120000</t>
   </si>
   <si>
     <t>Level</t>
@@ -498,7 +495,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -530,14 +527,6 @@
         <v>39</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B5" t="s" s="2">
         <v>37</v>
       </c>
     </row>
@@ -553,40 +542,40 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>41</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>42</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>38</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="F1" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="G1" t="s" s="1">
         <v>45</v>
-      </c>
-      <c r="G1" t="s" s="1">
-        <v>46</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="E2" t="s" s="2">
         <v>48</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>49</v>
       </c>
       <c r="F2" t="s" s="2">
         <v>15</v>
@@ -597,17 +586,17 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="E3" t="s" s="2">
         <v>50</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>51</v>
       </c>
       <c r="F3" t="s" s="2">
         <v>15</v>
@@ -618,17 +607,17 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="E4" t="s" s="2">
         <v>52</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>53</v>
       </c>
       <c r="F4" t="s" s="2">
         <v>15</v>
@@ -639,17 +628,17 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s" s="2">
         <v>54</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>55</v>
       </c>
       <c r="F5" t="s" s="2">
         <v>15</v>
